--- a/tools/importer/reports/import-footer.report.xlsx
+++ b/tools/importer/reports/import-footer.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-05T07:47:53.400Z</t>
+    <t>2026-10-06T10:02:08.500Z</t>
   </si>
   <si>
     <t>https://www.mgselect.co.in/</t>
@@ -70,10 +70,19 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-05T07:17:22.404Z</t>
+    <t>2026-10-05T09:00:48.495Z</t>
   </si>
   <si>
     <t>MG Latest Luxury &amp; Electric Cars in India - Prices &amp; Models</t>
+  </si>
+  <si>
+    <t>nav.report.json</t>
+  </si>
+  <si>
+    <t>nav</t>
+  </si>
+  <si>
+    <t>2026-10-06T10:01:59.133Z</t>
   </si>
 </sst>
 </file>
@@ -462,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -562,6 +571,35 @@
         <v>14</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
